--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_010/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_010/extracted.xlsx
@@ -279,6 +279,16 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="I3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -444,11 +454,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -519,6 +524,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G6" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -554,6 +564,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -585,11 +600,6 @@
       </text>
     </comment>
     <comment ref="F8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G8" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1356,12 +1366,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Conjugate heat transfer model for sizing liquid-cooled cold plate on Lunar Lander Power Distribution Unit</t>
+          <t>Conjugate heat transfer model for liquid-cooled cold plate sizing of the Lunar Lander Power Distribution Unit</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Predicts peak device junction temperatures and loop pressure drop for the PDU cold plate across the mission envelope (Re ≈ 3,500–9,000, 0.6–1.5 kW total heat, PAO-6 coolant at 15–45 °C inlet). Results support CDR design decisions for a space avionics thermal management system.</t>
+          <t>The CHT model predicts peak device junction temperatures and loop pressure drop for the PDU cold plate across the mission envelope (Re ≈ 3,500–9,000, heat input 0.6–1.5 kW, PAO-6 coolant inlet 15–45 °C). Results support CDR-level design decisions for thermal margin and pressure-drop sizing.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1389,15 +1399,19 @@
           <t>ASME-VV40-2018</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n"/>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>Thermal/Fluids Analysis Team</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md — LL-PDU CHT V&amp;V memo, Thermal/Fluids Analysis Team, 06 Aug 2026</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1516,7 +1530,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Peak Junction Temperature Limit</t>
+          <t>Peak Device Junction Temperature Limit</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1526,7 +1540,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Predicted P95 peak device junction temperature must remain below 85 °C across the worst credible mission operating envelope; pressure drop must also be bounded by loop map constraints.</t>
+          <t>Predicted P95 peak junction temperature must remain below 85 °C across the worst credible mission envelope; model result 78.9 °C provides a 6.1 °C margin.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1543,51 +1557,51 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>3D Conjugate Heat Transfer (CHT) Model — Rev C</t>
+          <t>Loop Pressure Drop Prediction Accuracy</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>ANSYS Fluent 2024R1 RANS (k–ω SST, low-Re) CHT model of the PDU cold plate; includes solid regions, TIM resistances, and radiation to 250 K sink; cross-checked against OpenFOAM v2312 chtMultiRegionFoam.</t>
+          <t>Model must predict loop ΔP within an acceptable tolerance to support pump sizing; demonstrated within 5% of TVAC measurement.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>TVAC Breadboard Test Dataset</t>
+          <t>ANSYS Fluent 2024R1 — 3D CHT / RANS k-ω SST Model</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Thermal-vacuum chamber test of cold plate breadboard with 27 in-situ-calibrated type-T thermocouples and FLIR A6750sc IR camera; archived as NI TDMS files in Windchill.</t>
+          <t>Poly-hexcore CHT model with k-ω SST (low-Re), y+ &lt; 1, radiation to 250 K sink, solid regions Al 6061-T6 / Cu / TIM, managed under SQA plan SP-CHT-004.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>PAO-6 Thermo-Physical Properties / TIM Coupon Data</t>
+          <t>OpenFOAM v2312 — chtMultiRegionFoam Cross-Check Model</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>PAO-6 fluid properties from AFIT dataset verified by bench viscometer/densitometer (±2%); Shin-Etsu X23 TIM through-thickness resistance from coupon measurements (0.2 ± 0.04 K·cm²/W); surface emissivity from IR reflectometer (ε = 0.78–0.82).</t>
+          <t>Independent open-source CHT solver used to reproduce Rev C results; agreed within 2.7 K peak temperature and 7% ΔP.</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1613,12 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Geometry — As-Built CMM Survey</t>
+          <t>TVAC Breadboard Test Dataset</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>CMM dimensional verification of Rev C cold plate flow passages showing deviations &lt; ±0.05 mm versus CAD; defeaturing per TFA-23 guideline documented.</t>
+          <t>27 type-T thermocouples (±0.5 K calibrated) and FLIR A6750sc IR camera data at 1.2 kW / 0.18 kg/s / 25 °C inlet; raw TDMS files and calibration sheets archived in Windchill.</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2055,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>TVAC Breadboard Thermal Correlation</t>
+          <t>TVAC Breadboard Temperature Correlation</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2056,12 +2070,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Cold plate breadboard tested in TVAC at 1.2 kW, 0.18 kg/s, 25 °C inlet. Model predictions compared to 27 thermocouple measurements and IR camera data. Two drifted TC channels excluded after calibration check. TIM resistance adjusted within measured coupon uncertainty only; no post-hoc fitting to TVAC data.</t>
+          <t>Cold plate breadboard tested in thermal-vacuum chamber; predicted versus measured device temperatures and loop pressure drop compared at 1.2 kW, 0.18 kg/s, 25 °C inlet.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>TVAC thermocouple and IR camera measurements (calibrated)</t>
+          <t>27 type-T thermocouple measurements and FLIR A6750sc IR camera imagery</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2071,7 +2085,7 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Measurement uncertainty characterisation (±0.5 K TC after in-situ calibration); input uncertainty via Latin Hypercube Sampling (500 samples)</t>
+          <t>Calibrated instrument uncertainty ±0.5 K; two drifted channels excluded after calibration check</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
@@ -2088,7 +2102,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Mesh Convergence / Grid Convergence Index Study</t>
+          <t>Heated Turbulent Channel Code Benchmark</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2098,27 +2112,22 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Three poly-hexcore meshes (2.1M, 4.8M, 9.6M cells) used to quantify spatial discretisation error via Grid Convergence Index (GCI) for peak device temperature and pressure drop.</t>
+          <t>ANSYS Fluent re-ran a heated turbulent channel flow at Reτ ≈ 395 and compared Nusselt number to literature to verify code physics.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / GCI formalism</t>
+          <t>Published literature Nusselt number for heated turbulent channel at Reτ ≈ 395</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Grid Convergence Index (GCI)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>GCI 1.8% for peak device temperature; GCI 3.5% for pressure drop</t>
+          <t>Nusselt number agreement within 2.3%</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2130,7 +2139,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Temporal Discretisation Sensitivity (Startup Transient)</t>
+          <t>Canonical Plate-to-Fluid CHT Benchmark</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2140,12 +2149,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Startup transient simulated with 0.1 s and 0.05 s time steps. Peak overshoot difference between the two step sizes assessed; steady-state used for sizing.</t>
+          <t>ANSYS Fluent ran a canonical plate-to-fluid CHT benchmark case and compared Nusselt number to literature.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Coarser vs. finer time-step results</t>
+          <t>Published literature Nusselt number for plate-to-fluid CHT case</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2155,7 +2164,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>Peak overshoot difference 0.6 K between step sizes</t>
+          <t>Nusselt number agreement within 3.1%</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2167,7 +2176,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Solver Code Verification — Benchmark Cases</t>
+          <t>Mesh Convergence / GCI Study</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2177,22 +2186,27 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>ANSYS Fluent 2024R1 re-run against heated turbulent channel (Reτ ≈ 395) and canonical plate-to-fluid CHT benchmark. Nusselt number compared to published literature.</t>
+          <t>Three poly-hexcore meshes (2.1M, 4.8M, 9.6M cells) used to quantify discretization error via Grid Convergence Index for peak device temperature and pressure drop.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Literature Nusselt number data</t>
+          <t>Richardson extrapolation / GCI methodology</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Grid Convergence Index (GCI)</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Turbulent channel Nu within 2.3%; plate CHT Nu within 3.1%</t>
+          <t>GCI 1.8% for peak device temperature; 3.5% for pressure drop</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2204,7 +2218,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Cross-Code Verification (OpenFOAM vs. Fluent)</t>
+          <t>Latin Hypercube Uncertainty Propagation</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2214,22 +2228,27 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>OpenFOAM v2312 (chtMultiRegionFoam) reproduced the Rev C Fluent solution using matching wall treatment for the same geometry and boundary conditions.</t>
+          <t>500-sample LHS Monte Carlo over measured input ranges (flow ±2%, heat ±1%, k_Al ±5%, k_TIM ±20%, emissivity ±0.05, roughness Ra 1–5 µm) to yield P95 peak temperature and sensitivity indices.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>ANSYS Fluent 2024R1 Rev C results</t>
+          <t>85 °C design limit</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Latin Hypercube Sampling (500 samples); Sobol sensitivity indices</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>Peak temperature within 2.7 K; ΔP within 7%</t>
+          <t>P95 peak device temperature 78.9 °C (6.1 °C margin); TIM accounts for 61% of variance, flow 24%</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2241,7 +2260,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>Latin Hypercube Uncertainty Propagation</t>
+          <t>OpenFOAM Cross-Code Check</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -2251,27 +2270,22 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>500-sample LHS over measured input ranges (flow ±2%, heat ±1%, k_Al ±5%, k_TIM ±20%, surface ε ±0.05, roughness Ra 1–5 µm). P95 peak junction temperature reported. Sobol indices computed for sensitivity ranking.</t>
+          <t>OpenFOAM v2312 chtMultiRegionFoam reproduced the Rev C Fluent case with matching wall treatment to verify code-independence of results.</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>85 °C thermal requirement</t>
+          <t>ANSYS Fluent 2024R1 Rev C predictions</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>Latin Hypercube Sampling (LHS), 500 samples; Sobol first-order sensitivity indices</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>P95 peak junction temperature 78.9 °C (margin 6.1 °C to 85 °C limit); TIM accounts for 61% of variance, flow 24%</t>
+          <t>Peak temperature within 2.7 K; ΔP within 7%</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
@@ -2425,12 +2439,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Simulation software shall be operated under a documented SQA plan with regression/benchmark testing and version control.</t>
+          <t>Commercial solver with documented SQA plan, version control, and regression smoke tests</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>ANSYS Fluent 2024R1 operated under SQA plan SP-CHT-004. Benchmark cases (turbulent channel, CHT plate) re-run and matched literature within ~3%. CI pipeline re-runs smoke cases on each commit. Meshes, case files, and scripts version-controlled in GitLab (tag LL-PDU-CHT_RevC) with DOORS traceability. Replay on a different workstation matched within 0.1 K.</t>
+          <t>ANSYS Fluent 2024R1 operated under SQA plan SP-CHT-004. Case files, meshes, and post-processing scripts version-controlled in GitLab (tag LL-PDU-CHT_RevC) with DOORS traceability. CI pipeline re-runs smoke cases on each commit. Analyst training certificates on file. OpenFOAM cross-check provides additional independent code confidence.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2459,12 +2473,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Code shall be verified against analytical solutions or well-established benchmarks for the relevant physics.</t>
+          <t>Benchmark against analytical or published solutions for relevant flow regime</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Fluent 2024R1 verified against heated turbulent channel (Reτ ≈ 395, Nu within 2.3%) and canonical plate-to-fluid CHT benchmark (Nu within 3.1%). Cross-code check against OpenFOAM v2312 chtMultiRegionFoam yielded peak temperature within 2.7 K and ΔP within 7%, providing independent confirmation that both codes solve the governing equations consistently.</t>
+          <t>Fluent re-ran a heated turbulent channel (Reτ ≈ 395) matching published Nusselt within 2.3%, and a canonical plate-to-fluid CHT case within 3.1%. Cross-code check with OpenFOAM v2312 reproduced peak temperature within 2.7 K and ΔP within 7%. Both benchmarks are relevant to the turbulent channel flow regime of the cold plate.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2493,12 +2507,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Spatial and temporal discretisation errors shall be quantified and shown to be small relative to margins.</t>
+          <t>Mesh convergence study with quantified GCI below 5% for primary QoIs</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three poly-hexcore meshes (2.1M, 4.8M, 9.6M cells) used with GCI analysis: GCI 1.8% for peak device temperature, 3.5% for ΔP. Second-order spatial discretisation throughout. Temporal sensitivity confirmed: 0.1 s vs. 0.05 s steps differ by only 0.6 K peak overshoot. Time resolution limits documented as acknowledged residual uncertainty.</t>
+          <t>Three poly-hexcore meshes (2.1M, 4.8M, 9.6M cells) used with second-order spatial/temporal discretization. GCI = 1.8% for peak device temperature and 3.5% for pressure drop — both below the 5% threshold. Transient time-step sensitivity (0.1 s vs 0.05 s) showed 0.6 K peak overshoot difference, documented. Global energy imbalance &lt; 0.1%.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2527,12 +2541,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Iterative solver shall be demonstrated to have converged with residuals at or below established targets.</t>
+          <t>Residuals below 1e-5; iterative error quantified</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Residuals driven below 1e-6; global energy imbalance &lt;0.1%. Iterative error estimated at &lt;0.2 K based on last-decade slope monitoring. Balance checks archived. No unphysical negative heat transfer coefficients observed during post-processing hygiene checks.</t>
+          <t>Residuals driven below 1e-6; global energy imbalance &lt; 0.1%. Iterative (solver) error estimated at &lt; 0.2 K from last-decade residual slope analysis. Convergence monitoring explicitly documented.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2561,12 +2575,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Model setup shall be independently reviewed for correct boundary conditions, geometry, and post-processing.</t>
+          <t>Independent review of model setup; boundary conditions and mesh quality verified</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Calculation checklist completed and signed by a different engineer. Independent Aero-Thermal Red Team walkthrough identified and corrected an erroneous emissivity assumption before TVAC; all action items closed. Area-weighted film coefficients, wall y+, and local Biot numbers monitored. Geometry defeaturing follows TFA-23 guideline; CMM comparison confirms &lt; ±0.05 mm deviations in flow passages. Replays on a different workstation matched within 0.1 K.</t>
+          <t>Aero-Thermal Red Team (independent of design line) conducted a walkthrough and identified an erroneous emissivity assumption that was corrected before TVAC. Calc-checklist signed by a different engineer. Wall y+, area-weighted film coefficients, local Biot numbers, and post-processing balance checks monitored and archived. No unphysical negative HTC observed. Replays on a different workstation matched within 0.1 K.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2595,12 +2609,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>The mathematical model and closure choices shall be justified for the physics regime of the COU.</t>
+          <t>Governing equations and closure models justified for the relevant physics regime; limitations documented</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>3D CHT with RANS k–ω SST (low-Re formulation) and y+ &lt; 1 near-wall resolution is appropriate for Re 3,500–9,000 turbulent internal flow. Solid regions correctly represented (Al 6061-T6, Cu, TIM as thin resistances). Radiation to 250 K sink included; buoyancy neglected with documented justification (microgravity, high Re). Known limitations (no boiling, no g-loads &gt;2 g, no cavitation, no contamination) explicitly bounded. Cross-code confirmation strengthens model form confidence.</t>
+          <t>3D CHT with RANS k-ω SST (low-Re formulation) and y+ &lt; 1 selected for the turbulent internal flow regime (Re 3,500–9,000). Radiation to 250 K sink (ε = 0.8) included; buoyancy neglected with documented justification (microgravity, high Re dominance). TIM modeled as thin resistances. Applicability bounds explicitly documented (single-phase PAO, Re range, no boiling, no g-loads &gt; 2 g, no cavitation). Known limitations stated.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2629,12 +2643,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties, boundary conditions, and geometry inputs shall be traceable to measurements with quantified uncertainties.</t>
+          <t>Material properties and boundary conditions from measured data with uncertainty characterization</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>PAO-6 properties from AFIT dataset verified by bench viscometer/densitometer (±2%). TIM resistance from coupon measurements (0.2 ± 0.04 K·cm²/W). Emissivity from portable IR reflectometer (ε = 0.78–0.82). Inlet mass flow ±2%, heat loads ±1% from calibrated meters. CMM confirms geometry &lt; ±0.05 mm. All uncertainties propagated through LHS UQ. Raw data, calibration sheets, and solver decks archived in Windchill with Monte Carlo seeds.</t>
+          <t>PAO-6 properties from AFIT dataset, verified by bench viscometer/densitometer within 2%. TIM resistance measured on coupons: 0.2 ± 0.04 K·cm²/W. Surface emissivity measured by IR reflectometer (ε = 0.78–0.82). Heat loads from electrical characterization (±1%). Inlet flow 0.12–0.24 kg/s pump-controlled. Geometry deviations from CMM &lt; ±0.05 mm in flow passages. All input uncertainties characterized and propagated.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2663,12 +2677,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test hardware shall be representative of the design with adequate instrumentation density.</t>
+          <t>Test article representative of design; characterization documented</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>One cold plate breadboard tested in TVAC. The breadboard is described as production-representative and instrumented with 27 type-T thermocouples (in-situ calibrated) and FLIR A6750sc IR camera. No multiple-specimen statistical characterisation reported; single article limits sample evidence to level 3. Two TC channels drifted and were excluded after calibration check, which was handled appropriately.</t>
+          <t>A single cold plate breadboard was tested in TVAC. The breadboard is described as representative of the Rev C design (CAD defeatured per TFA-23 guideline, CMM verified). No multiple specimens or statistical characterization of sample population is reported; sample size justification not explicit. Two TC channels drifted and were excluded after calibration verification. Adequate for CDR-level credibility given single breadboard nature.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2697,12 +2711,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test environment shall be controlled, instrumented, and traceable to calibrated standards with reported measurement uncertainty.</t>
+          <t>Calibrated instruments, controlled environment, measurement uncertainty quantified</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>TVAC test conducted in a controlled vacuum environment (10^-4 Pa). Thermocouples calibrated in-situ (±0.5 K). IR camera (FLIR A6750sc) used for field temperature mapping. Pump-controlled inlet mass flow with ±2% uncertainty. Heat loads from calibrated electrical meters (±1%). Calibration sheets archived in Windchill; test standard / ASTM reference not explicitly cited, but calibration traceability is well documented.</t>
+          <t>TVAC chamber at vacuum 10^-4 Pa; 27 type-T thermocouples calibrated in-situ (±0.5 K); FLIR A6750sc IR camera used as independent temperature check. Inlet flow and heat loads controlled and measured with ±2% and ±1% uncertainties respectively. Raw TDMS data, calibration sheets, and solver decks archived in Windchill. Two drifted TCs identified and excluded via calibration check. Conditions span the design operating range.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2731,12 +2745,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model inputs for the validation case shall match measured experimental conditions, with uncertainties propagated.</t>
+          <t>Model boundary conditions match TVAC test conditions; deviations quantified</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>TVAC test conditions (1.2 kW, 0.18 kg/s, 25 °C inlet) are directly mapped to model boundary conditions. Only TIM resistance was adjusted within measured coupon uncertainty bounds; no post-hoc fitting to TVAC data was performed. Input measurement uncertainties (flow ±2%, heat ±1%, materials) quantified and propagated through LHS. Equivalency between test and model inputs is explicitly documented and independently reviewed.</t>
+          <t>TVAC conditions (1.2 kW, 0.18 kg/s, 25 °C inlet) directly mapped to model boundary conditions. Heat loads from electrical characterization (±1%) and flow from pump-controlled measurements (±2%) used as model inputs matching test. TIM resistance adjusted only within measured coupon uncertainty bounds — explicitly not fitted to the TVAC system dataset. Input parameter comparison is explicit and separation of tuning from validation is documented.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2765,12 +2779,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Model predictions shall be quantitatively compared to experimental data at multiple locations with uncertainty bands reported.</t>
+          <t>Quantitative error metrics for primary QoIs; uncertainty bands reported</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Mean device temperature error 1.5 K; max local error 3.2 K across 27 thermocouple locations plus IR camera field data. Loop ΔP prediction within 5%. P95 peak junction temperature from LHS is 78.9 °C vs. 85 °C limit (6.1 °C margin). Sobol sensitivity indices quantify dominant contributors (TIM 61%, flow 24%). Tuning vs. check-out data separation explicitly maintained. Results archived and replicated on alternate workstation.</t>
+          <t>Mean device temperature error 1.5 K; maximum local error 3.2 K against 27-TC TVAC dataset. Loop ΔP within 5% of measurement. P95 peak temperature 78.9 °C vs 85 °C limit (6.1 °C margin) from 500-sample LHS. Sobol indices identify dominant uncertainty contributors (TIM 61%, flow 24%). Degraded-pump sensitivity case (−10% flow) keeps peak below 82.5 °C. Comparison covers both primary QoIs (temperature and pressure drop).</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2799,12 +2813,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>The model QoIs (peak junction temperature, loop pressure drop) shall directly address the safety and performance requirements and be measurable both computationally and experimentally.</t>
+          <t>QoIs directly address the thermal safety and sizing concern; measurable computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Peak device junction temperature directly compared to the 85 °C thermal limit; loop pressure drop compared to loop map constraints. Both QoIs are predicted by the model and measured in the TVAC test (thermocouples, IR camera, pressure instrumentation). LHS provides P95 statistics directly relevant to the requirement. Sobol indices tie sensitivity results back to dominant design parameters.</t>
+          <t>Primary QoIs are peak device junction temperature (directly compared to 85 °C limit) and loop ΔP (directly compared to pump sizing requirement). Both are predicted by the model and measured in TVAC. P95 temperature from UQ directly addresses the probabilistic margin question. Sobol sensitivity indices provide decision-relevant ranking of risk drivers. QoIs are fully aligned with the CDR design decision.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2833,12 +2847,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions shall span or bound the COU operating envelope; gaps shall be documented.</t>
+          <t>Validation conditions cover the full COU operating envelope; gaps documented</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>TVAC breadboard test was conducted at a single operating point (1.2 kW, 0.18 kg/s, 25 °C inlet) within the COU envelope (0.6–1.5 kW, 0.12–0.24 kg/s, 15–45 °C). LHS UQ propagates input variability across the full envelope, partially compensating for the single test point. Known gaps explicitly documented: g-loads &gt;2 g, cavitation, coolant contamination, and boiling not assessed. A full-stack system-level thermal balance test is planned but not yet complete. Applicability limits are bounded and communicated.</t>
+          <t>TVAC correlation was performed at a single operating point (1.2 kW, 0.18 kg/s, 25 °C inlet), which is representative but does not cover the full COU envelope (Re 3,500–9,000, heat 0.6–1.5 kW, inlet 15–45 °C). LHS UQ explores the envelope analytically. System-level thermal balance test with full avionics stack is planned but not yet complete. Known gaps (g-loads &gt; 2 g, cavitation, coolant contamination, pump wear-out, filter fouling) are explicitly documented. Geometry is production-representative per CMM verification. Adequate for CDR with documented next steps.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -3023,7 +3037,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The Rev C CHT model meets all credibility requirements for CDR-level design decisions within the stated operating window (Re 3,500–9,000, 0.6–1.5 kW, PAO-6 at 15–45 °C inlet). The P95 peak junction temperature of 78.9 °C provides a 6.1 °C margin to the 85 °C limit, supported by quantified numerical uncertainties (GCI 1.8%), validated against TVAC measurements (mean error 1.5 K, max 3.2 K), and independently reviewed by the Aero-Thermal Red Team. All 13 credibility factors are assessed at level 3 or above against MRL 3 requirements. Accepted with conditions: (1) a system-level full-stack thermal balance test shall be completed to validate device-to-base contact and enclosure radiation modeling before flight qualification; (2) UQ shall be extended to include pump wear-out drift and filter fouling; and (3) applicability is limited to single-phase PAO-6 within the documented envelope — use outside these bounds requires reassessment.</t>
+          <t>The Rev C CHT analysis set demonstrates adequate credibility for CDR-level design decisions within the stated operating envelope (Re 3,500–9,000, heat 0.6–1.5 kW, PAO-6 inlet 15–45 °C). The P95 peak junction temperature of 78.9 °C provides a 6.1 °C margin against the 85 °C limit, with quantified numerical errors (GCI 1.8%, iterative error &lt; 0.2 K) that are small relative to this margin. TVAC correlation shows mean temperature error of 1.5 K and ΔP within 5%. All 13 credibility factors are assessed at level 3 or higher. Residual limitations — single TVAC operating point, no system-level stack test, unassessed off-nominal conditions — are explicitly bounded and documented, with a plan to extend UQ and conduct a system-level balance test. No open red flags exist for CDR acceptance. Acceptance is conditioned on: (1) completion of the system-level avionics stack thermal balance test prior to PDR/CDR closure, (2) extension of UQ to include pump wear-out drift and filter fouling, and (3) re-evaluation of model credibility if operating conditions exceed the stated applicability bounds.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -3033,7 +3047,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Thermal/Fluids Analysis Team</t>
+          <t>Thermal/Fluids Analysis Team (reviewed by Aero-Thermal Red Team)</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
